--- a/data/preliminaries/stellar/male/18-preliminary-r04-stellar-male.xlsx
+++ b/data/preliminaries/stellar/male/18-preliminary-r04-stellar-male.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第四轮" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'赛事数据'!$A$1:$I$57</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,60 +415,49 @@
   </sheetPr>
   <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>组别</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>组内排名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>全局排名</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>头像</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>得票数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -486,11 +469,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,8 +495,10 @@
           <t>小野大辅</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>611</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,11 +512,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -545,8 +538,10 @@
           <t>神谷浩史</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>555</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -560,11 +555,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>11</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -582,12 +581,14 @@
           <t>石川英郎</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>477</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -597,11 +598,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>14</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -619,12 +624,14 @@
           <t>田丸笃志</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>470</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -634,11 +641,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>21</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -656,12 +667,14 @@
           <t>内田直哉</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>402</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -671,11 +684,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -689,12 +706,14 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>360</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -704,11 +723,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>28</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -726,12 +749,14 @@
           <t>松冈祯丞</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>351</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -741,11 +766,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>34</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -763,12 +792,14 @@
           <t>堀江瞬</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>299</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -778,11 +809,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>38</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -800,8 +835,10 @@
           <t>熊井统子</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>269</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -815,11 +852,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="n">
-        <v>40</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -837,8 +878,10 @@
           <t>加藤涉</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>248</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -852,11 +895,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="n">
-        <v>45</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -870,8 +917,10 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>193</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -885,11 +934,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="n">
-        <v>46</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -907,8 +960,10 @@
           <t>小林裕介</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>188</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -922,11 +977,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>54</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -940,8 +999,10 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>88</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -955,11 +1016,15 @@
           <t>男子5组</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="n">
-        <v>56</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -973,8 +1038,10 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>23</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -988,11 +1055,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1010,8 +1081,10 @@
           <t>下野纮</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>535</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1025,11 +1098,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>8</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1047,8 +1124,10 @@
           <t>森川智之</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>489</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1062,11 +1141,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="n">
-        <v>9</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1084,12 +1167,14 @@
           <t>井上和彦</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>486</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1099,11 +1184,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>19</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1121,12 +1210,14 @@
           <t>梶裕贵</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>422</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1227,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>22</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1154,12 +1249,14 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
-        <v>400</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1169,11 +1266,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" t="n">
-        <v>23</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1187,12 +1288,14 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>400</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1202,11 +1305,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" t="n">
-        <v>27</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1224,12 +1331,14 @@
           <t>间岛淳司</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>352</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1239,11 +1348,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" t="n">
-        <v>29</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1257,12 +1370,14 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>345</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1272,11 +1387,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>9</v>
-      </c>
-      <c r="C24" t="n">
-        <v>31</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1294,8 +1413,10 @@
           <t>松冈祯丞</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>335</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1309,11 +1430,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>10</v>
-      </c>
-      <c r="C25" t="n">
-        <v>35</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1331,8 +1456,10 @@
           <t>伊濑茉莉也</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>289</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1346,11 +1473,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>11</v>
-      </c>
-      <c r="C26" t="n">
-        <v>36</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1368,8 +1499,10 @@
           <t>潘惠美</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>288</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1383,11 +1516,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>12</v>
-      </c>
-      <c r="C27" t="n">
-        <v>44</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1405,8 +1542,10 @@
           <t>梶裕贵</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>210</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,11 +1559,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>13</v>
-      </c>
-      <c r="C28" t="n">
-        <v>51</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1438,8 +1581,10 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>106</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1453,11 +1598,15 @@
           <t>男子6组</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>14</v>
-      </c>
-      <c r="C29" t="n">
-        <v>52</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1471,8 +1620,10 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>106</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1486,11 +1637,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1508,8 +1663,10 @@
           <t>杉山纪彰</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>576</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1523,11 +1680,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" t="n">
-        <v>7</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1545,8 +1706,10 @@
           <t>岛崎信长</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>511</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1560,11 +1723,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="n">
-        <v>10</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1582,12 +1749,14 @@
           <t>中村悠一</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>486</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1597,11 +1766,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="n">
-        <v>16</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1619,12 +1792,14 @@
           <t>福山润</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>435</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1634,11 +1809,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="n">
-        <v>17</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1656,12 +1835,14 @@
           <t>关智一</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>432</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1852,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" t="n">
-        <v>20</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1693,12 +1878,14 @@
           <t>石毛翔弥</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>422</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1708,11 +1895,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>7</v>
-      </c>
-      <c r="C36" t="n">
-        <v>25</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1730,12 +1921,14 @@
           <t>野泽雅子</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>378</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1745,11 +1938,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>8</v>
-      </c>
-      <c r="C37" t="n">
-        <v>32</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1767,12 +1964,14 @@
           <t>醍醐虎汰朗</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>334</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1782,11 +1981,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>9</v>
-      </c>
-      <c r="C38" t="n">
-        <v>39</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1800,8 +2003,10 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
-        <v>262</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1815,11 +2020,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>10</v>
-      </c>
-      <c r="C39" t="n">
-        <v>41</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1837,8 +2046,10 @@
           <t>内田雄马</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>248</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1852,11 +2063,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>11</v>
-      </c>
-      <c r="C40" t="n">
-        <v>42</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1874,8 +2089,10 @@
           <t>内田雄马</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>239</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1889,11 +2106,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C41" t="n">
-        <v>47</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1907,8 +2128,10 @@
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
-        <v>188</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1922,11 +2145,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>13</v>
-      </c>
-      <c r="C42" t="n">
-        <v>48</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1944,8 +2171,10 @@
           <t>千叶翔也</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>166</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1959,11 +2188,15 @@
           <t>男子7组</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>14</v>
-      </c>
-      <c r="C43" t="n">
-        <v>53</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1977,8 +2210,10 @@
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="n">
-        <v>96</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1992,11 +2227,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2014,8 +2253,10 @@
           <t>内匠靖明</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>677</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2029,11 +2270,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="n">
-        <v>6</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2051,8 +2296,10 @@
           <t>福岛润</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>531</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2066,11 +2313,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>12</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2088,12 +2339,14 @@
           <t>小野贤章</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>475</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2356,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="n">
-        <v>13</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2125,12 +2382,14 @@
           <t>内山昂辉</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>472</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2140,11 +2399,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>15</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2162,12 +2425,14 @@
           <t>绪方惠美</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>466</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2177,11 +2442,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" t="n">
-        <v>18</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2199,12 +2468,14 @@
           <t>小松未可子</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>427</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2214,11 +2485,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>7</v>
-      </c>
-      <c r="C50" t="n">
-        <v>24</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2236,12 +2511,14 @@
           <t>榎木淳弥</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>393</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2251,11 +2528,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="n">
-        <v>30</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2269,12 +2550,14 @@
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>342</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2284,11 +2567,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>33</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2306,8 +2593,10 @@
           <t>阪口大助</t>
         </is>
       </c>
-      <c r="H52" t="n">
-        <v>314</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2321,11 +2610,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>10</v>
-      </c>
-      <c r="C53" t="n">
-        <v>37</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2339,8 +2632,10 @@
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
-        <v>277</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2354,11 +2649,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>11</v>
-      </c>
-      <c r="C54" t="n">
-        <v>43</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2372,8 +2671,10 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>229</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2387,11 +2688,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>12</v>
-      </c>
-      <c r="C55" t="n">
-        <v>49</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2409,8 +2714,10 @@
           <t>花江夏树</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>157</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2424,11 +2731,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>13</v>
-      </c>
-      <c r="C56" t="n">
-        <v>50</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2446,8 +2757,10 @@
           <t>诹访部顺一</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>124</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2461,11 +2774,15 @@
           <t>男子8组</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>14</v>
-      </c>
-      <c r="C57" t="n">
-        <v>55</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2483,8 +2800,10 @@
           <t>小野友树</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>84</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2493,7 +2812,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>